--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01057361720630214</v>
+        <v>0.009885283087319596</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01057361720630214</v>
+        <v>0.009885283087319596</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0103582933654372</v>
+        <v>0.009654554568931179</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0103582933654372</v>
+        <v>0.009654554568931179</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01014816620273668</v>
+        <v>0.009441743927621475</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01014816620273668</v>
+        <v>0.009441743927621475</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01016427570911671</v>
+        <v>0.009468292999280724</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01016427570911671</v>
+        <v>0.009468292999280724</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01065157043049357</v>
+        <v>0.009966376396170495</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01065157043049357</v>
+        <v>0.009966376396170495</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01177861847261864</v>
+        <v>0.0110920312494542</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01177861847261864</v>
+        <v>0.0110920312494542</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01372762245361283</v>
+        <v>0.01301203796495095</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01372762245361283</v>
+        <v>0.01301203796495095</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01650661426518829</v>
+        <v>0.01572340449922457</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01650661426518829</v>
+        <v>0.01572340449922457</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01989448843132472</v>
+        <v>0.01899817444512108</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01989448843132472</v>
+        <v>0.01899817444512108</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02363820526082747</v>
+        <v>0.02257508818056667</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02363820526082747</v>
+        <v>0.02257508818056667</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02746571686072164</v>
+        <v>0.02618702693640219</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02746571686072164</v>
+        <v>0.02618702693640219</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0312827888300151</v>
+        <v>0.02975805742068591</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0312827888300151</v>
+        <v>0.02975805742068591</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03553680699159392</v>
+        <v>0.03374768835544693</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03553680699159392</v>
+        <v>0.03374768835544693</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04036615953227013</v>
+        <v>0.03831096903010138</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04036615953227013</v>
+        <v>0.03831096903010138</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04557371953000385</v>
+        <v>0.04326974584105399</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04557371953000385</v>
+        <v>0.04326974584105399</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05077408028422714</v>
+        <v>0.04824516491351811</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05077408028422714</v>
+        <v>0.04824516491351811</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05543420319584878</v>
+        <v>0.05271799438679958</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05543420319584878</v>
+        <v>0.05271799438679958</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05974360813141773</v>
+        <v>0.05685317339203683</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05974360813141773</v>
+        <v>0.05685317339203683</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06330386349667455</v>
+        <v>0.06026755217781197</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06330386349667455</v>
+        <v>0.06026755217781197</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0660164815671193</v>
+        <v>0.06286089528136451</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0660164815671193</v>
+        <v>0.06286089528136451</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0678632169309366</v>
+        <v>0.06461043065253567</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0678632169309366</v>
+        <v>0.06461043065253567</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06904247125694354</v>
+        <v>0.06572135528950501</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06904247125694354</v>
+        <v>0.06572135528950501</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06997293922794197</v>
+        <v>0.06658373505033321</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06997293922794197</v>
+        <v>0.06658373505033321</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.07006398010107862</v>
+        <v>0.06665199098467742</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07006398010107862</v>
+        <v>0.06665199098467742</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06971365877832067</v>
+        <v>0.06630710678249614</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06971365877832067</v>
+        <v>0.06630710678249614</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.06905531853593753</v>
+        <v>0.06566915150410553</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06905531853593753</v>
+        <v>0.06566915150410553</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.06795082180215198</v>
+        <v>0.06464915317642464</v>
       </c>
       <c r="C28" t="n">
-        <v>0.06795082180215198</v>
+        <v>0.06464915317642464</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.06720086911732354</v>
+        <v>0.06396194650833528</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06720086911732354</v>
+        <v>0.06396194650833528</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.06528778597625549</v>
+        <v>0.06209177041203947</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06528778597625549</v>
+        <v>0.06209177041203947</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0639837161283386</v>
+        <v>0.06088121222632881</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0639837161283386</v>
+        <v>0.06088121222632881</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
